--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127103104</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127103076</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103616</v>
+        <v>127103351</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683466</v>
+        <v>683491</v>
       </c>
       <c r="R5" t="n">
-        <v>6688023</v>
+        <v>6687978</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127103351</v>
+        <v>127103616</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683491</v>
+        <v>683466</v>
       </c>
       <c r="R6" t="n">
-        <v>6687978</v>
+        <v>6688023</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1186,7 +1186,7 @@
         <v>127102827</v>
       </c>
       <c r="B7" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127103523</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>127102872</v>
       </c>
       <c r="B9" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127103504</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>127103375</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>127103201</v>
       </c>
       <c r="B12" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>127103575</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127103471</v>
+        <v>127103562</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>98414</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>683469</v>
+        <v>683478</v>
       </c>
       <c r="R14" t="n">
-        <v>6687995</v>
+        <v>6688036</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127103562</v>
+        <v>127103471</v>
       </c>
       <c r="B15" t="n">
-        <v>98339</v>
+        <v>98436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>683478</v>
+        <v>683469</v>
       </c>
       <c r="R15" t="n">
-        <v>6688036</v>
+        <v>6687995</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2068,7 +2068,7 @@
         <v>127103541</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>127103414</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>127102929</v>
       </c>
       <c r="B18" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127103294</v>
       </c>
       <c r="B19" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,32 +2453,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127103023</v>
+        <v>127103342</v>
       </c>
       <c r="B20" t="n">
-        <v>98278</v>
+        <v>98436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,13 +2488,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>683556</v>
+        <v>683494</v>
       </c>
       <c r="R20" t="n">
-        <v>6687968</v>
+        <v>6687970</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127103342</v>
+        <v>127103023</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>98353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>683494</v>
+        <v>683556</v>
       </c>
       <c r="R21" t="n">
-        <v>6687970</v>
+        <v>6687968</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127103104</v>
       </c>
       <c r="B3" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127103076</v>
       </c>
       <c r="B4" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127103351</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>127103616</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>127102827</v>
       </c>
       <c r="B7" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,45 +1280,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127103523</v>
+        <v>127102872</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98420</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683503</v>
+        <v>683545</v>
       </c>
       <c r="R8" t="n">
-        <v>6687998</v>
+        <v>6687974</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1377,54 +1386,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127102872</v>
+        <v>127103523</v>
       </c>
       <c r="B9" t="n">
-        <v>98414</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683545</v>
+        <v>683503</v>
       </c>
       <c r="R9" t="n">
-        <v>6687974</v>
+        <v>6687998</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1486,7 +1486,7 @@
         <v>127103504</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>127103375</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,10 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127103201</v>
+        <v>127103575</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>683529</v>
+        <v>683479</v>
       </c>
       <c r="R12" t="n">
-        <v>6687992</v>
+        <v>6688009</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127103575</v>
+        <v>127103201</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>683479</v>
+        <v>683529</v>
       </c>
       <c r="R13" t="n">
-        <v>6688009</v>
+        <v>6687992</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1874,7 +1874,7 @@
         <v>127103562</v>
       </c>
       <c r="B14" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>127103471</v>
       </c>
       <c r="B15" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>127103541</v>
       </c>
       <c r="B16" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>127103414</v>
       </c>
       <c r="B17" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>127102929</v>
       </c>
       <c r="B18" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127103294</v>
       </c>
       <c r="B19" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,32 +2453,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127103342</v>
+        <v>127103023</v>
       </c>
       <c r="B20" t="n">
-        <v>98436</v>
+        <v>98359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,13 +2488,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>683494</v>
+        <v>683556</v>
       </c>
       <c r="R20" t="n">
-        <v>6687970</v>
+        <v>6687968</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127103023</v>
+        <v>127103342</v>
       </c>
       <c r="B21" t="n">
-        <v>98353</v>
+        <v>98442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>683556</v>
+        <v>683494</v>
       </c>
       <c r="R21" t="n">
-        <v>6687968</v>
+        <v>6687970</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127102929</v>
+        <v>127103294</v>
       </c>
       <c r="B18" t="n">
-        <v>98465</v>
+        <v>98442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683548</v>
+        <v>683498</v>
       </c>
       <c r="R18" t="n">
-        <v>6687980</v>
+        <v>6687961</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2356,32 +2356,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127103294</v>
+        <v>127102929</v>
       </c>
       <c r="B19" t="n">
-        <v>98442</v>
+        <v>98465</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683498</v>
+        <v>683548</v>
       </c>
       <c r="R19" t="n">
-        <v>6687961</v>
+        <v>6687980</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2453,32 +2453,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127103023</v>
+        <v>127103342</v>
       </c>
       <c r="B20" t="n">
-        <v>98359</v>
+        <v>98442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,13 +2488,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>683556</v>
+        <v>683494</v>
       </c>
       <c r="R20" t="n">
-        <v>6687968</v>
+        <v>6687970</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127103342</v>
+        <v>127103023</v>
       </c>
       <c r="B21" t="n">
-        <v>98442</v>
+        <v>98359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>683494</v>
+        <v>683556</v>
       </c>
       <c r="R21" t="n">
-        <v>6687970</v>
+        <v>6687968</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127103076</v>
+        <v>127103351</v>
       </c>
       <c r="B4" t="n">
-        <v>98420</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683546</v>
+        <v>683491</v>
       </c>
       <c r="R4" t="n">
-        <v>6687968</v>
+        <v>6687978</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,7 +989,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103351</v>
+        <v>127103616</v>
       </c>
       <c r="B5" t="n">
         <v>98442</v>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683491</v>
+        <v>683466</v>
       </c>
       <c r="R5" t="n">
-        <v>6687978</v>
+        <v>6688023</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127103616</v>
+        <v>127103076</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>98420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683466</v>
+        <v>683546</v>
       </c>
       <c r="R6" t="n">
-        <v>6688023</v>
+        <v>6687968</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1280,54 +1280,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127102872</v>
+        <v>127103523</v>
       </c>
       <c r="B8" t="n">
-        <v>98420</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683545</v>
+        <v>683503</v>
       </c>
       <c r="R8" t="n">
-        <v>6687974</v>
+        <v>6687998</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,45 +1377,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103523</v>
+        <v>127102872</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683503</v>
+        <v>683545</v>
       </c>
       <c r="R9" t="n">
-        <v>6687998</v>
+        <v>6687974</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127103294</v>
+        <v>127102929</v>
       </c>
       <c r="B18" t="n">
-        <v>98442</v>
+        <v>98465</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683498</v>
+        <v>683548</v>
       </c>
       <c r="R18" t="n">
-        <v>6687961</v>
+        <v>6687980</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2356,32 +2356,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127102929</v>
+        <v>127103294</v>
       </c>
       <c r="B19" t="n">
-        <v>98465</v>
+        <v>98442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683548</v>
+        <v>683498</v>
       </c>
       <c r="R19" t="n">
-        <v>6687980</v>
+        <v>6687961</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127103104</v>
       </c>
       <c r="B3" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127103351</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127103616</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>127103076</v>
       </c>
       <c r="B6" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>127102827</v>
       </c>
       <c r="B7" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127103523</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>127102872</v>
       </c>
       <c r="B9" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127103504</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>127103375</v>
       </c>
       <c r="B11" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>127103575</v>
       </c>
       <c r="B12" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>127103201</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>127103562</v>
       </c>
       <c r="B14" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>127103471</v>
       </c>
       <c r="B15" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>127103541</v>
       </c>
       <c r="B16" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>127103414</v>
       </c>
       <c r="B17" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127102929</v>
+        <v>127103294</v>
       </c>
       <c r="B18" t="n">
-        <v>98465</v>
+        <v>98443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683548</v>
+        <v>683498</v>
       </c>
       <c r="R18" t="n">
-        <v>6687980</v>
+        <v>6687961</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2356,32 +2356,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127103294</v>
+        <v>127102929</v>
       </c>
       <c r="B19" t="n">
-        <v>98442</v>
+        <v>98466</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683498</v>
+        <v>683548</v>
       </c>
       <c r="R19" t="n">
-        <v>6687961</v>
+        <v>6687980</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2456,7 +2456,7 @@
         <v>127103342</v>
       </c>
       <c r="B20" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127103023</v>
       </c>
       <c r="B21" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127103562</v>
+        <v>127103471</v>
       </c>
       <c r="B14" t="n">
-        <v>98421</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>683478</v>
+        <v>683469</v>
       </c>
       <c r="R14" t="n">
-        <v>6688036</v>
+        <v>6687995</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127103471</v>
+        <v>127103562</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>98421</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>683469</v>
+        <v>683478</v>
       </c>
       <c r="R15" t="n">
-        <v>6687995</v>
+        <v>6688036</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127103351</v>
+        <v>127103076</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98421</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683491</v>
+        <v>683546</v>
       </c>
       <c r="R4" t="n">
-        <v>6687978</v>
+        <v>6687968</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1086,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127103076</v>
+        <v>127103351</v>
       </c>
       <c r="B6" t="n">
-        <v>98421</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683546</v>
+        <v>683491</v>
       </c>
       <c r="R6" t="n">
-        <v>6687968</v>
+        <v>6687978</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1280,45 +1280,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127103523</v>
+        <v>127102872</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>98421</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683503</v>
+        <v>683545</v>
       </c>
       <c r="R8" t="n">
-        <v>6687998</v>
+        <v>6687974</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1377,54 +1386,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127102872</v>
+        <v>127103523</v>
       </c>
       <c r="B9" t="n">
-        <v>98421</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683545</v>
+        <v>683503</v>
       </c>
       <c r="R9" t="n">
-        <v>6687974</v>
+        <v>6687998</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127103504</v>
+        <v>127103375</v>
       </c>
       <c r="B10" t="n">
         <v>98443</v>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683476</v>
+        <v>683487</v>
       </c>
       <c r="R10" t="n">
-        <v>6688014</v>
+        <v>6687976</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127103375</v>
+        <v>127103504</v>
       </c>
       <c r="B11" t="n">
         <v>98443</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683487</v>
+        <v>683476</v>
       </c>
       <c r="R11" t="n">
-        <v>6687976</v>
+        <v>6688014</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127103294</v>
+        <v>127102929</v>
       </c>
       <c r="B18" t="n">
-        <v>98443</v>
+        <v>98466</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683498</v>
+        <v>683548</v>
       </c>
       <c r="R18" t="n">
-        <v>6687961</v>
+        <v>6687980</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2356,32 +2356,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127102929</v>
+        <v>127103294</v>
       </c>
       <c r="B19" t="n">
-        <v>98466</v>
+        <v>98443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683548</v>
+        <v>683498</v>
       </c>
       <c r="R19" t="n">
-        <v>6687980</v>
+        <v>6687961</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2453,32 +2453,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127103342</v>
+        <v>127103023</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,13 +2488,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>683494</v>
+        <v>683556</v>
       </c>
       <c r="R20" t="n">
-        <v>6687970</v>
+        <v>6687968</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127103023</v>
+        <v>127103342</v>
       </c>
       <c r="B21" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>683556</v>
+        <v>683494</v>
       </c>
       <c r="R21" t="n">
-        <v>6687968</v>
+        <v>6687970</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127103471</v>
+        <v>127103562</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>98421</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>683469</v>
+        <v>683478</v>
       </c>
       <c r="R14" t="n">
-        <v>6687995</v>
+        <v>6688036</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127103562</v>
+        <v>127103471</v>
       </c>
       <c r="B15" t="n">
-        <v>98421</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>683478</v>
+        <v>683469</v>
       </c>
       <c r="R15" t="n">
-        <v>6688036</v>
+        <v>6687995</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127103104</v>
       </c>
       <c r="B3" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127103076</v>
+        <v>127103616</v>
       </c>
       <c r="B4" t="n">
-        <v>98421</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683546</v>
+        <v>683466</v>
       </c>
       <c r="R4" t="n">
-        <v>6687968</v>
+        <v>6688023</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103616</v>
+        <v>127103351</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683466</v>
+        <v>683491</v>
       </c>
       <c r="R5" t="n">
-        <v>6688023</v>
+        <v>6687978</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127103351</v>
+        <v>127103076</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98425</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683491</v>
+        <v>683546</v>
       </c>
       <c r="R6" t="n">
-        <v>6687978</v>
+        <v>6687968</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1186,7 +1186,7 @@
         <v>127102827</v>
       </c>
       <c r="B7" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127102872</v>
       </c>
       <c r="B8" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>127103523</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127103375</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>127103504</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,10 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127103575</v>
+        <v>127103201</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>683479</v>
+        <v>683529</v>
       </c>
       <c r="R12" t="n">
-        <v>6688009</v>
+        <v>6687992</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127103201</v>
+        <v>127103575</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>683529</v>
+        <v>683479</v>
       </c>
       <c r="R13" t="n">
-        <v>6687992</v>
+        <v>6688009</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1874,7 +1874,7 @@
         <v>127103562</v>
       </c>
       <c r="B14" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>127103471</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>127103541</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>127103414</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127102929</v>
+        <v>127103294</v>
       </c>
       <c r="B18" t="n">
-        <v>98466</v>
+        <v>98447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683548</v>
+        <v>683498</v>
       </c>
       <c r="R18" t="n">
-        <v>6687980</v>
+        <v>6687961</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2356,32 +2356,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127103294</v>
+        <v>127102929</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>98470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683498</v>
+        <v>683548</v>
       </c>
       <c r="R19" t="n">
-        <v>6687961</v>
+        <v>6687980</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2456,7 +2456,7 @@
         <v>127103023</v>
       </c>
       <c r="B20" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127103342</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -989,32 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103351</v>
+        <v>127103076</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683491</v>
+        <v>683546</v>
       </c>
       <c r="R5" t="n">
-        <v>6687978</v>
+        <v>6687968</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127103076</v>
+        <v>127103351</v>
       </c>
       <c r="B6" t="n">
-        <v>98425</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683546</v>
+        <v>683491</v>
       </c>
       <c r="R6" t="n">
-        <v>6687968</v>
+        <v>6687978</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1280,54 +1280,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127102872</v>
+        <v>127103523</v>
       </c>
       <c r="B8" t="n">
-        <v>98425</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683545</v>
+        <v>683503</v>
       </c>
       <c r="R8" t="n">
-        <v>6687974</v>
+        <v>6687998</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,45 +1377,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103523</v>
+        <v>127102872</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>98425</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683503</v>
+        <v>683545</v>
       </c>
       <c r="R9" t="n">
-        <v>6687998</v>
+        <v>6687974</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127103375</v>
+        <v>127103504</v>
       </c>
       <c r="B10" t="n">
         <v>98447</v>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683487</v>
+        <v>683476</v>
       </c>
       <c r="R10" t="n">
-        <v>6687976</v>
+        <v>6688014</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127103504</v>
+        <v>127103375</v>
       </c>
       <c r="B11" t="n">
         <v>98447</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683476</v>
+        <v>683487</v>
       </c>
       <c r="R11" t="n">
-        <v>6688014</v>
+        <v>6687976</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127103201</v>
+        <v>127103575</v>
       </c>
       <c r="B12" t="n">
         <v>98447</v>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>683529</v>
+        <v>683479</v>
       </c>
       <c r="R12" t="n">
-        <v>6687992</v>
+        <v>6688009</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127103575</v>
+        <v>127103201</v>
       </c>
       <c r="B13" t="n">
         <v>98447</v>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>683479</v>
+        <v>683529</v>
       </c>
       <c r="R13" t="n">
-        <v>6688009</v>
+        <v>6687992</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -1280,45 +1280,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127103523</v>
+        <v>127102872</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>98425</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683503</v>
+        <v>683545</v>
       </c>
       <c r="R8" t="n">
-        <v>6687998</v>
+        <v>6687974</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1377,54 +1386,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127102872</v>
+        <v>127103523</v>
       </c>
       <c r="B9" t="n">
-        <v>98425</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683545</v>
+        <v>683503</v>
       </c>
       <c r="R9" t="n">
-        <v>6687974</v>
+        <v>6687998</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127103616</v>
+        <v>127103076</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683466</v>
+        <v>683546</v>
       </c>
       <c r="R4" t="n">
-        <v>6688023</v>
+        <v>6687968</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,32 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103076</v>
+        <v>127103351</v>
       </c>
       <c r="B5" t="n">
-        <v>98425</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683546</v>
+        <v>683491</v>
       </c>
       <c r="R5" t="n">
-        <v>6687968</v>
+        <v>6687978</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,7 +1086,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127103351</v>
+        <v>127103616</v>
       </c>
       <c r="B6" t="n">
         <v>98447</v>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683491</v>
+        <v>683466</v>
       </c>
       <c r="R6" t="n">
-        <v>6687978</v>
+        <v>6688023</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127103294</v>
+        <v>127102929</v>
       </c>
       <c r="B18" t="n">
-        <v>98447</v>
+        <v>98470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683498</v>
+        <v>683548</v>
       </c>
       <c r="R18" t="n">
-        <v>6687961</v>
+        <v>6687980</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2356,32 +2356,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127102929</v>
+        <v>127103294</v>
       </c>
       <c r="B19" t="n">
-        <v>98470</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683548</v>
+        <v>683498</v>
       </c>
       <c r="R19" t="n">
-        <v>6687980</v>
+        <v>6687961</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127103104</v>
       </c>
       <c r="B3" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127103076</v>
       </c>
       <c r="B4" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127103351</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>127103616</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>127102827</v>
       </c>
       <c r="B7" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,54 +1280,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127102872</v>
+        <v>127103523</v>
       </c>
       <c r="B8" t="n">
-        <v>98425</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683545</v>
+        <v>683503</v>
       </c>
       <c r="R8" t="n">
-        <v>6687974</v>
+        <v>6687998</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,45 +1377,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103523</v>
+        <v>127102872</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>98426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683503</v>
+        <v>683545</v>
       </c>
       <c r="R9" t="n">
-        <v>6687998</v>
+        <v>6687974</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1486,7 +1486,7 @@
         <v>127103504</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>127103375</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>127103575</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>127103201</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127103562</v>
+        <v>127103471</v>
       </c>
       <c r="B14" t="n">
-        <v>98425</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>683478</v>
+        <v>683469</v>
       </c>
       <c r="R14" t="n">
-        <v>6688036</v>
+        <v>6687995</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127103471</v>
+        <v>127103562</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>98426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>683469</v>
+        <v>683478</v>
       </c>
       <c r="R15" t="n">
-        <v>6687995</v>
+        <v>6688036</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2068,7 +2068,7 @@
         <v>127103541</v>
       </c>
       <c r="B16" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>127103414</v>
       </c>
       <c r="B17" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>127102929</v>
       </c>
       <c r="B18" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127103294</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,32 +2453,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127103023</v>
+        <v>127103342</v>
       </c>
       <c r="B20" t="n">
-        <v>98364</v>
+        <v>98448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,13 +2488,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>683556</v>
+        <v>683494</v>
       </c>
       <c r="R20" t="n">
-        <v>6687968</v>
+        <v>6687970</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127103342</v>
+        <v>127103023</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>98365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>683494</v>
+        <v>683556</v>
       </c>
       <c r="R21" t="n">
-        <v>6687970</v>
+        <v>6687968</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127103076</v>
+        <v>127103351</v>
       </c>
       <c r="B4" t="n">
-        <v>98426</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683546</v>
+        <v>683491</v>
       </c>
       <c r="R4" t="n">
-        <v>6687968</v>
+        <v>6687978</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,7 +989,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103351</v>
+        <v>127103616</v>
       </c>
       <c r="B5" t="n">
         <v>98448</v>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683491</v>
+        <v>683466</v>
       </c>
       <c r="R5" t="n">
-        <v>6687978</v>
+        <v>6688023</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127103616</v>
+        <v>127103076</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>98426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683466</v>
+        <v>683546</v>
       </c>
       <c r="R6" t="n">
-        <v>6688023</v>
+        <v>6687968</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127103104</v>
       </c>
       <c r="B3" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127103351</v>
+        <v>127103616</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683491</v>
+        <v>683466</v>
       </c>
       <c r="R4" t="n">
-        <v>6687978</v>
+        <v>6688023</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,32 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103616</v>
+        <v>127103076</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683466</v>
+        <v>683546</v>
       </c>
       <c r="R5" t="n">
-        <v>6688023</v>
+        <v>6687968</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127103076</v>
+        <v>127103351</v>
       </c>
       <c r="B6" t="n">
-        <v>98426</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683546</v>
+        <v>683491</v>
       </c>
       <c r="R6" t="n">
-        <v>6687968</v>
+        <v>6687978</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1186,7 +1186,7 @@
         <v>127102827</v>
       </c>
       <c r="B7" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,45 +1280,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127103523</v>
+        <v>127102872</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>98428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683503</v>
+        <v>683545</v>
       </c>
       <c r="R8" t="n">
-        <v>6687998</v>
+        <v>6687974</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1377,54 +1386,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127102872</v>
+        <v>127103523</v>
       </c>
       <c r="B9" t="n">
-        <v>98426</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683545</v>
+        <v>683503</v>
       </c>
       <c r="R9" t="n">
-        <v>6687974</v>
+        <v>6687998</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1486,7 +1486,7 @@
         <v>127103504</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>127103375</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,10 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127103575</v>
+        <v>127103201</v>
       </c>
       <c r="B12" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>683479</v>
+        <v>683529</v>
       </c>
       <c r="R12" t="n">
-        <v>6688009</v>
+        <v>6687992</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127103201</v>
+        <v>127103575</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>683529</v>
+        <v>683479</v>
       </c>
       <c r="R13" t="n">
-        <v>6687992</v>
+        <v>6688009</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127103471</v>
+        <v>127103562</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>683469</v>
+        <v>683478</v>
       </c>
       <c r="R14" t="n">
-        <v>6687995</v>
+        <v>6688036</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127103562</v>
+        <v>127103471</v>
       </c>
       <c r="B15" t="n">
-        <v>98426</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>683478</v>
+        <v>683469</v>
       </c>
       <c r="R15" t="n">
-        <v>6688036</v>
+        <v>6687995</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2068,7 +2068,7 @@
         <v>127103541</v>
       </c>
       <c r="B16" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>127103414</v>
       </c>
       <c r="B17" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>127102929</v>
       </c>
       <c r="B18" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127103294</v>
       </c>
       <c r="B19" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,32 +2453,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127103342</v>
+        <v>127103023</v>
       </c>
       <c r="B20" t="n">
-        <v>98448</v>
+        <v>98367</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,13 +2488,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>683494</v>
+        <v>683556</v>
       </c>
       <c r="R20" t="n">
-        <v>6687970</v>
+        <v>6687968</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127103023</v>
+        <v>127103342</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>98450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>683556</v>
+        <v>683494</v>
       </c>
       <c r="R21" t="n">
-        <v>6687968</v>
+        <v>6687970</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -892,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127103616</v>
+        <v>127103351</v>
       </c>
       <c r="B4" t="n">
         <v>98450</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683466</v>
+        <v>683491</v>
       </c>
       <c r="R4" t="n">
-        <v>6688023</v>
+        <v>6687978</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,32 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103076</v>
+        <v>127103616</v>
       </c>
       <c r="B5" t="n">
-        <v>98428</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683546</v>
+        <v>683466</v>
       </c>
       <c r="R5" t="n">
-        <v>6687968</v>
+        <v>6688023</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127103351</v>
+        <v>127103076</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683491</v>
+        <v>683546</v>
       </c>
       <c r="R6" t="n">
-        <v>6687978</v>
+        <v>6687968</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1280,54 +1280,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127102872</v>
+        <v>127103523</v>
       </c>
       <c r="B8" t="n">
-        <v>98428</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683545</v>
+        <v>683503</v>
       </c>
       <c r="R8" t="n">
-        <v>6687974</v>
+        <v>6687998</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,45 +1377,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103523</v>
+        <v>127102872</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683503</v>
+        <v>683545</v>
       </c>
       <c r="R9" t="n">
-        <v>6687998</v>
+        <v>6687974</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127103201</v>
+        <v>127103575</v>
       </c>
       <c r="B12" t="n">
         <v>98450</v>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>683529</v>
+        <v>683479</v>
       </c>
       <c r="R12" t="n">
-        <v>6687992</v>
+        <v>6688009</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127103575</v>
+        <v>127103201</v>
       </c>
       <c r="B13" t="n">
         <v>98450</v>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>683479</v>
+        <v>683529</v>
       </c>
       <c r="R13" t="n">
-        <v>6688009</v>
+        <v>6687992</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -1280,45 +1280,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127103523</v>
+        <v>127102872</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>98428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683503</v>
+        <v>683545</v>
       </c>
       <c r="R8" t="n">
-        <v>6687998</v>
+        <v>6687974</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1377,54 +1386,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127102872</v>
+        <v>127103523</v>
       </c>
       <c r="B9" t="n">
-        <v>98428</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683545</v>
+        <v>683503</v>
       </c>
       <c r="R9" t="n">
-        <v>6687974</v>
+        <v>6687998</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -2453,32 +2453,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127103023</v>
+        <v>127103342</v>
       </c>
       <c r="B20" t="n">
-        <v>98367</v>
+        <v>98450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,13 +2488,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>683556</v>
+        <v>683494</v>
       </c>
       <c r="R20" t="n">
-        <v>6687968</v>
+        <v>6687970</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127103342</v>
+        <v>127103023</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>98367</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>683494</v>
+        <v>683556</v>
       </c>
       <c r="R21" t="n">
-        <v>6687970</v>
+        <v>6687968</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127103351</v>
+        <v>127103076</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683491</v>
+        <v>683546</v>
       </c>
       <c r="R4" t="n">
-        <v>6687978</v>
+        <v>6687968</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,7 +989,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103616</v>
+        <v>127103351</v>
       </c>
       <c r="B5" t="n">
         <v>98450</v>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683466</v>
+        <v>683491</v>
       </c>
       <c r="R5" t="n">
-        <v>6688023</v>
+        <v>6687978</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127103076</v>
+        <v>127103616</v>
       </c>
       <c r="B6" t="n">
-        <v>98428</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683546</v>
+        <v>683466</v>
       </c>
       <c r="R6" t="n">
-        <v>6687968</v>
+        <v>6688023</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1280,54 +1280,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127102872</v>
+        <v>127103523</v>
       </c>
       <c r="B8" t="n">
-        <v>98428</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683545</v>
+        <v>683503</v>
       </c>
       <c r="R8" t="n">
-        <v>6687974</v>
+        <v>6687998</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,45 +1377,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103523</v>
+        <v>127102872</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683503</v>
+        <v>683545</v>
       </c>
       <c r="R9" t="n">
-        <v>6687998</v>
+        <v>6687974</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127103504</v>
+        <v>127103375</v>
       </c>
       <c r="B10" t="n">
         <v>98450</v>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683476</v>
+        <v>683487</v>
       </c>
       <c r="R10" t="n">
-        <v>6688014</v>
+        <v>6687976</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127103375</v>
+        <v>127103504</v>
       </c>
       <c r="B11" t="n">
         <v>98450</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683487</v>
+        <v>683476</v>
       </c>
       <c r="R11" t="n">
-        <v>6687976</v>
+        <v>6688014</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127103104</v>
       </c>
       <c r="B3" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127103076</v>
+        <v>127103351</v>
       </c>
       <c r="B4" t="n">
-        <v>98428</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683546</v>
+        <v>683491</v>
       </c>
       <c r="R4" t="n">
-        <v>6687968</v>
+        <v>6687978</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103351</v>
+        <v>127103616</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683491</v>
+        <v>683466</v>
       </c>
       <c r="R5" t="n">
-        <v>6687978</v>
+        <v>6688023</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127103616</v>
+        <v>127103076</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683466</v>
+        <v>683546</v>
       </c>
       <c r="R6" t="n">
-        <v>6688023</v>
+        <v>6687968</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1186,7 +1186,7 @@
         <v>127102827</v>
       </c>
       <c r="B7" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127103523</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>127102872</v>
       </c>
       <c r="B9" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127103375</v>
+        <v>127103504</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683487</v>
+        <v>683476</v>
       </c>
       <c r="R10" t="n">
-        <v>6687976</v>
+        <v>6688014</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127103504</v>
+        <v>127103375</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683476</v>
+        <v>683487</v>
       </c>
       <c r="R11" t="n">
-        <v>6688014</v>
+        <v>6687976</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1680,7 +1680,7 @@
         <v>127103575</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>127103201</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127103562</v>
+        <v>127103471</v>
       </c>
       <c r="B14" t="n">
-        <v>98428</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>683478</v>
+        <v>683469</v>
       </c>
       <c r="R14" t="n">
-        <v>6688036</v>
+        <v>6687995</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127103471</v>
+        <v>127103562</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>98434</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>683469</v>
+        <v>683478</v>
       </c>
       <c r="R15" t="n">
-        <v>6687995</v>
+        <v>6688036</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2068,7 +2068,7 @@
         <v>127103541</v>
       </c>
       <c r="B16" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>127103414</v>
       </c>
       <c r="B17" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127102929</v>
+        <v>127103294</v>
       </c>
       <c r="B18" t="n">
-        <v>98473</v>
+        <v>98456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683548</v>
+        <v>683498</v>
       </c>
       <c r="R18" t="n">
-        <v>6687980</v>
+        <v>6687961</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2356,32 +2356,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127103294</v>
+        <v>127102929</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>98479</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683498</v>
+        <v>683548</v>
       </c>
       <c r="R19" t="n">
-        <v>6687961</v>
+        <v>6687980</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2456,7 +2456,7 @@
         <v>127103342</v>
       </c>
       <c r="B20" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127103023</v>
       </c>
       <c r="B21" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127103104</v>
       </c>
       <c r="B3" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127103351</v>
+        <v>127103076</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683491</v>
+        <v>683546</v>
       </c>
       <c r="R4" t="n">
-        <v>6687978</v>
+        <v>6687968</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103616</v>
+        <v>127103351</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683466</v>
+        <v>683491</v>
       </c>
       <c r="R5" t="n">
-        <v>6688023</v>
+        <v>6687978</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127103076</v>
+        <v>127103616</v>
       </c>
       <c r="B6" t="n">
-        <v>98434</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683546</v>
+        <v>683466</v>
       </c>
       <c r="R6" t="n">
-        <v>6687968</v>
+        <v>6688023</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1186,7 +1186,7 @@
         <v>127102827</v>
       </c>
       <c r="B7" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127103523</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>127102872</v>
       </c>
       <c r="B9" t="n">
-        <v>98434</v>
+        <v>98437</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127103504</v>
       </c>
       <c r="B10" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>127103375</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>127103575</v>
       </c>
       <c r="B12" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>127103201</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,32 +1871,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127103471</v>
+        <v>127103562</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98437</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>683469</v>
+        <v>683478</v>
       </c>
       <c r="R14" t="n">
-        <v>6687995</v>
+        <v>6688036</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127103562</v>
+        <v>127103471</v>
       </c>
       <c r="B15" t="n">
-        <v>98434</v>
+        <v>98459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>683478</v>
+        <v>683469</v>
       </c>
       <c r="R15" t="n">
-        <v>6688036</v>
+        <v>6687995</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2068,7 +2068,7 @@
         <v>127103541</v>
       </c>
       <c r="B16" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>127103414</v>
       </c>
       <c r="B17" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127103294</v>
+        <v>127102929</v>
       </c>
       <c r="B18" t="n">
-        <v>98456</v>
+        <v>98482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683498</v>
+        <v>683548</v>
       </c>
       <c r="R18" t="n">
-        <v>6687961</v>
+        <v>6687980</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2356,32 +2356,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127102929</v>
+        <v>127103294</v>
       </c>
       <c r="B19" t="n">
-        <v>98479</v>
+        <v>98459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683548</v>
+        <v>683498</v>
       </c>
       <c r="R19" t="n">
-        <v>6687980</v>
+        <v>6687961</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2456,7 +2456,7 @@
         <v>127103342</v>
       </c>
       <c r="B20" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>127103023</v>
       </c>
       <c r="B21" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127103104</v>
       </c>
       <c r="B3" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127103076</v>
       </c>
       <c r="B4" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127103351</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>127103616</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>127102827</v>
       </c>
       <c r="B7" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,45 +1280,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127103523</v>
+        <v>127102872</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>98445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683503</v>
+        <v>683545</v>
       </c>
       <c r="R8" t="n">
-        <v>6687998</v>
+        <v>6687974</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1377,54 +1386,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127102872</v>
+        <v>127103523</v>
       </c>
       <c r="B9" t="n">
-        <v>98437</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683545</v>
+        <v>683503</v>
       </c>
       <c r="R9" t="n">
-        <v>6687974</v>
+        <v>6687998</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1486,7 +1486,7 @@
         <v>127103504</v>
       </c>
       <c r="B10" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>127103375</v>
       </c>
       <c r="B11" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>127103575</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>127103201</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>127103562</v>
       </c>
       <c r="B14" t="n">
-        <v>98437</v>
+        <v>98445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>127103471</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>127103541</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>127103414</v>
       </c>
       <c r="B17" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>127102929</v>
       </c>
       <c r="B18" t="n">
-        <v>98482</v>
+        <v>98490</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127103294</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,32 +2453,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127103342</v>
+        <v>127103023</v>
       </c>
       <c r="B20" t="n">
-        <v>98459</v>
+        <v>98384</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,13 +2488,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>683494</v>
+        <v>683556</v>
       </c>
       <c r="R20" t="n">
-        <v>6687970</v>
+        <v>6687968</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127103023</v>
+        <v>127103342</v>
       </c>
       <c r="B21" t="n">
-        <v>98376</v>
+        <v>98467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>683556</v>
+        <v>683494</v>
       </c>
       <c r="R21" t="n">
-        <v>6687968</v>
+        <v>6687970</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127103104</v>
       </c>
       <c r="B3" t="n">
-        <v>98445</v>
+        <v>98414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127103076</v>
       </c>
       <c r="B4" t="n">
-        <v>98445</v>
+        <v>98414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127103351</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>127103616</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>127102827</v>
       </c>
       <c r="B7" t="n">
-        <v>98445</v>
+        <v>98414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,54 +1280,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127102872</v>
+        <v>127103523</v>
       </c>
       <c r="B8" t="n">
-        <v>98445</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683545</v>
+        <v>683503</v>
       </c>
       <c r="R8" t="n">
-        <v>6687974</v>
+        <v>6687998</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,45 +1377,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103523</v>
+        <v>127102872</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>98414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683503</v>
+        <v>683545</v>
       </c>
       <c r="R9" t="n">
-        <v>6687998</v>
+        <v>6687974</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1486,7 +1486,7 @@
         <v>127103504</v>
       </c>
       <c r="B10" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>127103375</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,10 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127103575</v>
+        <v>127103201</v>
       </c>
       <c r="B12" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>683479</v>
+        <v>683529</v>
       </c>
       <c r="R12" t="n">
-        <v>6688009</v>
+        <v>6687992</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127103201</v>
+        <v>127103575</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>683529</v>
+        <v>683479</v>
       </c>
       <c r="R13" t="n">
-        <v>6687992</v>
+        <v>6688009</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1874,7 +1874,7 @@
         <v>127103562</v>
       </c>
       <c r="B14" t="n">
-        <v>98445</v>
+        <v>98414</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>127103471</v>
       </c>
       <c r="B15" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>127103541</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>127103414</v>
       </c>
       <c r="B17" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>127102929</v>
       </c>
       <c r="B18" t="n">
-        <v>98490</v>
+        <v>98459</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>127103294</v>
       </c>
       <c r="B19" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,32 +2453,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127103023</v>
+        <v>127103342</v>
       </c>
       <c r="B20" t="n">
-        <v>98384</v>
+        <v>98436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,13 +2488,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>683556</v>
+        <v>683494</v>
       </c>
       <c r="R20" t="n">
-        <v>6687968</v>
+        <v>6687970</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127103342</v>
+        <v>127103023</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>98353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>683494</v>
+        <v>683556</v>
       </c>
       <c r="R21" t="n">
-        <v>6687970</v>
+        <v>6687968</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>111352133</v>
       </c>
       <c r="B2" t="n">
-        <v>88909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683515.9013629078</v>
+        <v>683516</v>
       </c>
       <c r="R2" t="n">
-        <v>6687964.030537949</v>
+        <v>6687964</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -795,48 +790,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127103104</v>
+        <v>112834202</v>
       </c>
       <c r="B3" t="n">
-        <v>98445</v>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Igelsjö, Igelsjö, Upl</t>
+          <t>Norrskedika, norr om Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>683527</v>
+        <v>683234</v>
       </c>
       <c r="R3" t="n">
-        <v>6687975</v>
+        <v>6687880</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,22 +875,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Elin Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127103076</v>
+        <v>127103023</v>
       </c>
       <c r="B4" t="n">
-        <v>98445</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +902,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,7 +926,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683546</v>
+        <v>683556</v>
       </c>
       <c r="R4" t="n">
         <v>6687968</v>
@@ -989,48 +988,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103351</v>
+        <v>112834209</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>99096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Igelsjö, Igelsjö, Upl</t>
+          <t>Norrskedika, norr om Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683491</v>
+        <v>683570</v>
       </c>
       <c r="R5" t="n">
-        <v>6687978</v>
+        <v>6687957</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,12 +1053,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1074,44 +1073,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Elin Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127103616</v>
+        <v>127102827</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>99096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683466</v>
+        <v>683523</v>
       </c>
       <c r="R6" t="n">
-        <v>6688023</v>
+        <v>6687960</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1183,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127102827</v>
+        <v>127102872</v>
       </c>
       <c r="B7" t="n">
-        <v>98445</v>
+        <v>99096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,17 +1214,26 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>683523</v>
+        <v>683545</v>
       </c>
       <c r="R7" t="n">
-        <v>6687960</v>
+        <v>6687974</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1280,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127102872</v>
+        <v>127103076</v>
       </c>
       <c r="B8" t="n">
-        <v>98445</v>
+        <v>99096</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,26 +1320,17 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683545</v>
+        <v>683546</v>
       </c>
       <c r="R8" t="n">
-        <v>6687974</v>
+        <v>6687968</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,32 +1389,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103523</v>
+        <v>127103104</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>99096</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683503</v>
+        <v>683527</v>
       </c>
       <c r="R9" t="n">
-        <v>6687998</v>
+        <v>6687975</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1483,32 +1486,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127103504</v>
+        <v>127103562</v>
       </c>
       <c r="B10" t="n">
-        <v>98467</v>
+        <v>99096</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683476</v>
+        <v>683478</v>
       </c>
       <c r="R10" t="n">
-        <v>6688014</v>
+        <v>6688036</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1580,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127103375</v>
+        <v>127102929</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>99142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683487</v>
+        <v>683548</v>
       </c>
       <c r="R11" t="n">
-        <v>6687976</v>
+        <v>6687980</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1677,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127103575</v>
+        <v>127102609</v>
       </c>
       <c r="B12" t="n">
-        <v>98467</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1712,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>683479</v>
+        <v>683424</v>
       </c>
       <c r="R12" t="n">
-        <v>6688009</v>
+        <v>6687976</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1777,7 +1780,7 @@
         <v>127103201</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,32 +1874,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127103562</v>
+        <v>127103294</v>
       </c>
       <c r="B14" t="n">
-        <v>98445</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>683478</v>
+        <v>683498</v>
       </c>
       <c r="R14" t="n">
-        <v>6688036</v>
+        <v>6687961</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1968,10 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127103471</v>
+        <v>127103342</v>
       </c>
       <c r="B15" t="n">
-        <v>98467</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,13 +2006,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>683469</v>
+        <v>683494</v>
       </c>
       <c r="R15" t="n">
-        <v>6687995</v>
+        <v>6687970</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2065,10 +2068,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127103541</v>
+        <v>127103351</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>683489</v>
+        <v>683491</v>
       </c>
       <c r="R16" t="n">
-        <v>6688011</v>
+        <v>6687978</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2162,10 +2165,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127103414</v>
+        <v>127103375</v>
       </c>
       <c r="B17" t="n">
-        <v>98467</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,10 +2200,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>683477</v>
+        <v>683487</v>
       </c>
       <c r="R17" t="n">
-        <v>6687996</v>
+        <v>6687976</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2259,32 +2262,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127102929</v>
+        <v>127103414</v>
       </c>
       <c r="B18" t="n">
-        <v>98490</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2297,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683548</v>
+        <v>683477</v>
       </c>
       <c r="R18" t="n">
-        <v>6687980</v>
+        <v>6687996</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2356,10 +2359,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127103294</v>
+        <v>127103471</v>
       </c>
       <c r="B19" t="n">
-        <v>98467</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2391,10 +2394,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683498</v>
+        <v>683469</v>
       </c>
       <c r="R19" t="n">
-        <v>6687961</v>
+        <v>6687995</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2453,32 +2456,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127103023</v>
+        <v>127103504</v>
       </c>
       <c r="B20" t="n">
-        <v>98384</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2488,10 +2491,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>683556</v>
+        <v>683476</v>
       </c>
       <c r="R20" t="n">
-        <v>6687968</v>
+        <v>6688014</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2550,10 +2553,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127103342</v>
+        <v>127103523</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,13 +2588,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>683494</v>
+        <v>683503</v>
       </c>
       <c r="R21" t="n">
-        <v>6687970</v>
+        <v>6687998</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2644,6 +2647,297 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127103541</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Igelsjö, Igelsjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>683489</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6688011</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127103575</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Igelsjö, Igelsjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>683479</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6688009</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127103616</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Igelsjö, Igelsjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>683466</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6688023</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111352133</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112834202</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103023</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112834209</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127102827</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127102872</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103076</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103104</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103562</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127102929</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1774,6 +1829,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127102609</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1871,6 +1931,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103201</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103294</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2065,6 +2135,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103342</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,6 +2237,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103351</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2259,6 +2339,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103375</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2356,6 +2441,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103414</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2453,6 +2543,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103471</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2550,6 +2645,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103504</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2647,6 +2747,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103523</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2744,6 +2849,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103541</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2841,6 +2951,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103575</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2938,8 +3053,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103616</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>